--- a/Result/profitability/5478.xlsx
+++ b/Result/profitability/5478.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.04</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9575</v>
+        <v>2.01625</v>
       </c>
       <c r="N2" t="n">
-        <v>54.175</v>
+        <v>55.17625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>1.90375</v>
+        <v>2.0125</v>
       </c>
       <c r="N3" t="n">
-        <v>55.49625</v>
+        <v>56.49375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.81</v>
       </c>
       <c r="M4" t="n">
-        <v>2.07375</v>
+        <v>2.18</v>
       </c>
       <c r="N4" t="n">
-        <v>57.2975</v>
+        <v>58.1125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.12125</v>
+        <v>2.07625</v>
       </c>
       <c r="N5" t="n">
-        <v>58.20249999999999</v>
+        <v>58.705</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2.09875</v>
+        <v>2.1775</v>
       </c>
       <c r="N6" t="n">
-        <v>59.13875</v>
+        <v>59.96875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>2.10625</v>
+        <v>2.135</v>
       </c>
       <c r="N7" t="n">
-        <v>60.31375</v>
+        <v>60.96375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1075</v>
+        <v>2.09875</v>
       </c>
       <c r="N8" t="n">
-        <v>61.09375</v>
+        <v>61.46375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>2.2075</v>
       </c>
       <c r="N12" t="n">
-        <v>59.99124999999999</v>
+        <v>59.99125</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5478</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1680</v>
+      </c>
+      <c r="D75" t="n">
+        <v>689</v>
+      </c>
+      <c r="E75" t="n">
+        <v>992</v>
+      </c>
+      <c r="F75" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="G75" t="n">
+        <v>367</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>21.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>82</v>
+      </c>
+      <c r="J75" t="n">
+        <v>449</v>
+      </c>
+      <c r="K75" t="n">
+        <v>345</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.9925</v>
+      </c>
+      <c r="N75" t="n">
+        <v>53.84375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.07000000000000028</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.02928870292887042</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.960000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05280999107939333</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.3600000000000003</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1343283582089554</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.019999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07310420076377522</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
